--- a/backend/medical_store/test-result.xlsx
+++ b/backend/medical_store/test-result.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="35">
   <si>
     <t>Test Name</t>
   </si>
@@ -162,7 +162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="17.36328125"/>
@@ -322,6 +322,142 @@
         <v>27</v>
       </c>
       <c r="E9" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s" s="0">
         <v>22</v>
       </c>
     </row>
@@ -340,7 +476,7 @@
         <v>30</v>
       </c>
       <c r="B1" t="n" s="0">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="2">
@@ -348,7 +484,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="3">
